--- a/115課表.xlsx
+++ b/115課表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1D789F-49B7-4AD6-AD32-E73FBFF7C3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7125441-3AA0-4B58-B1B3-523CD4680F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4104" yWindow="3720" windowWidth="11544" windowHeight="9960" xr2:uid="{3C16C183-FE85-484E-8D03-1ED68A655D3A}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{3C16C183-FE85-484E-8D03-1ED68A655D3A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,163 +39,242 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="74">
+  <si>
+    <t>一-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一-2</t>
+  </si>
+  <si>
+    <t>一-3</t>
+  </si>
+  <si>
+    <t>一-4</t>
+  </si>
+  <si>
+    <t>一-5</t>
+  </si>
+  <si>
+    <t>一-6</t>
+  </si>
+  <si>
+    <t>一-7</t>
+  </si>
+  <si>
+    <t>二-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二-2</t>
+  </si>
+  <si>
+    <t>二-3</t>
+  </si>
+  <si>
+    <t>二-4</t>
+  </si>
+  <si>
+    <t>二-5</t>
+  </si>
+  <si>
+    <t>二-6</t>
+  </si>
+  <si>
+    <t>二-7</t>
+  </si>
+  <si>
+    <t>三-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三-2</t>
+  </si>
+  <si>
+    <t>三-3</t>
+  </si>
+  <si>
+    <t>三-4</t>
+  </si>
+  <si>
+    <t>三-5</t>
+  </si>
+  <si>
+    <t>三-6</t>
+  </si>
+  <si>
+    <t>三-7</t>
+  </si>
+  <si>
+    <t>四-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四-2</t>
+  </si>
+  <si>
+    <t>四-3</t>
+  </si>
+  <si>
+    <t>四-4</t>
+  </si>
+  <si>
+    <t>四-5</t>
+  </si>
+  <si>
+    <t>四-6</t>
+  </si>
+  <si>
+    <t>四-7</t>
+  </si>
+  <si>
+    <t>五-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五-2</t>
+  </si>
+  <si>
+    <t>五-3</t>
+  </si>
+  <si>
+    <t>五-4</t>
+  </si>
+  <si>
+    <t>五-5</t>
+  </si>
+  <si>
+    <t>五-6</t>
+  </si>
+  <si>
+    <t>五-7</t>
+  </si>
+  <si>
+    <t>班級</t>
+  </si>
+  <si>
+    <t>農騰虎嘯</t>
+  </si>
+  <si>
+    <t>地理</t>
+  </si>
+  <si>
+    <t>生物</t>
+  </si>
+  <si>
+    <t>自然</t>
+  </si>
+  <si>
+    <t>風馳電掣</t>
+  </si>
+  <si>
+    <t>數學</t>
+  </si>
+  <si>
+    <t>健教</t>
+  </si>
+  <si>
+    <t>音樂</t>
+  </si>
+  <si>
+    <t>表演藝術</t>
+  </si>
+  <si>
+    <t>英文</t>
+  </si>
+  <si>
+    <t>輔導</t>
+  </si>
+  <si>
+    <t>品味生活</t>
+  </si>
+  <si>
+    <t>家政</t>
+  </si>
+  <si>
+    <t>童軍</t>
+  </si>
+  <si>
+    <t>歷史</t>
+  </si>
+  <si>
+    <t>全球化</t>
+  </si>
+  <si>
+    <t>公民</t>
+  </si>
+  <si>
+    <t>生活科技</t>
+  </si>
+  <si>
+    <t>資訊科技</t>
+  </si>
+  <si>
+    <t>學校自治</t>
+  </si>
+  <si>
+    <t>國文</t>
+  </si>
+  <si>
+    <t>本土語</t>
+  </si>
+  <si>
+    <t>體育</t>
+  </si>
+  <si>
+    <t>視覺藝術</t>
+  </si>
+  <si>
+    <t>人文風光</t>
+  </si>
+  <si>
+    <t>一-8</t>
+  </si>
+  <si>
+    <t>數學</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二-8</t>
+  </si>
+  <si>
+    <t>社會</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>國文</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>英文</t>
+    <t>社團活動</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>數學</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一-2</t>
-  </si>
-  <si>
-    <t>一-3</t>
-  </si>
-  <si>
-    <t>一-4</t>
-  </si>
-  <si>
-    <t>一-5</t>
-  </si>
-  <si>
-    <t>一-6</t>
-  </si>
-  <si>
-    <t>一-7</t>
-  </si>
-  <si>
-    <t>一-8</t>
-  </si>
-  <si>
-    <t>二-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二-2</t>
-  </si>
-  <si>
-    <t>二-3</t>
-  </si>
-  <si>
-    <t>二-4</t>
-  </si>
-  <si>
-    <t>二-5</t>
-  </si>
-  <si>
-    <t>二-6</t>
-  </si>
-  <si>
-    <t>二-7</t>
-  </si>
-  <si>
-    <t>二-8</t>
-  </si>
-  <si>
-    <t>三-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三-2</t>
-  </si>
-  <si>
-    <t>三-3</t>
-  </si>
-  <si>
-    <t>三-4</t>
-  </si>
-  <si>
-    <t>三-5</t>
-  </si>
-  <si>
-    <t>三-6</t>
-  </si>
-  <si>
-    <t>三-7</t>
-  </si>
-  <si>
-    <t>三-8</t>
-  </si>
-  <si>
-    <t>四-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>四-2</t>
-  </si>
-  <si>
-    <t>四-3</t>
-  </si>
-  <si>
-    <t>四-4</t>
-  </si>
-  <si>
-    <t>四-5</t>
-  </si>
-  <si>
-    <t>四-6</t>
-  </si>
-  <si>
-    <t>四-7</t>
-  </si>
-  <si>
-    <t>四-8</t>
-  </si>
-  <si>
-    <t>五-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>五-2</t>
-  </si>
-  <si>
-    <t>五-3</t>
-  </si>
-  <si>
-    <t>五-4</t>
-  </si>
-  <si>
-    <t>五-5</t>
-  </si>
-  <si>
-    <t>五-6</t>
-  </si>
-  <si>
-    <t>五-7</t>
-  </si>
-  <si>
-    <t>五-8</t>
   </si>
   <si>
     <t>生物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>人文風光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>自然</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>公民</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>歷史</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>四-8</t>
+  </si>
+  <si>
+    <t>五-8</t>
   </si>
 </sst>
 </file>
@@ -592,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923858C6-B215-4074-BF7A-7515DAB56C75}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -624,805 +703,805 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="G3" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H3" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
         <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
         <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="G12" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s">
         <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H18" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="G19" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="H19" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H20" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G23" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H23" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G24" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F25" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="H25" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H26" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E27" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G27" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="H27" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F28" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="G28" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H28" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F29" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="G29" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G31" t="s">
         <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G32" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H32" t="s">
         <v>46</v>
@@ -1430,239 +1509,245 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G33" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H33" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E34" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G34" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H34" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F35" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="G35" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="H35" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E36" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G36" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="H36" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s">
         <v>38</v>
       </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H37" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" t="s">
         <v>39</v>
-      </c>
-      <c r="B38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" t="s">
-        <v>44</v>
-      </c>
-      <c r="G38" t="s">
-        <v>44</v>
-      </c>
-      <c r="H38" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H39" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F40" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G41" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H41" t="s">
-        <v>47</v>
-      </c>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J2:N289">
+    <sortCondition ref="M1:M289"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
